--- a/cards_dataset/EN/BLACK_cards.xlsx
+++ b/cards_dataset/EN/BLACK_cards.xlsx
@@ -1,221 +1,477 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\2 Set up LLM\codigo_ollama\cards_dataset\EN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\!Master\Tesis\3 Mejorar codigo\Cards_Against_AI\cards_dataset\EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AAA7404-F3FA-42C1-B801-6204D2FA9713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3479621A-B4AB-4A33-977D-EA65F8BAB851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="texts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Card_Text</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
+  <si>
+    <t>B001</t>
   </si>
   <si>
     <t>It's a pity that kids these days are all getting involved with _______.</t>
   </si>
   <si>
+    <t>B002</t>
+  </si>
+  <si>
     <t>TFL apologizes for the delay in train service due to _______.</t>
   </si>
   <si>
+    <t>B003</t>
+  </si>
+  <si>
+    <t>Do NOT go here! Found _______ in my spaghetti bolognese!</t>
+  </si>
+  <si>
+    <t>B004</t>
+  </si>
+  <si>
     <t>Nobody expects the Spanish Inquisition. Our chief weapons are fear, surprise, and _______.</t>
   </si>
   <si>
-    <t>_______ + _______ = _______ (PICK 3)</t>
+    <t>B006</t>
   </si>
   <si>
     <t>Military historians remember Alexander the Great for his brilliant use of _______ against the Persians.</t>
   </si>
   <si>
+    <t>B007</t>
+  </si>
+  <si>
+    <t>What are my parents hiding from me? _______.</t>
+  </si>
+  <si>
+    <t>B008</t>
+  </si>
+  <si>
     <t>Coming to the West End this year, _______: The Musical.</t>
   </si>
   <si>
+    <t>B009</t>
+  </si>
+  <si>
     <t>Life for American Indians was forever changed when the White Man introduced them to _______.</t>
   </si>
   <si>
+    <t>B010</t>
+  </si>
+  <si>
+    <t>What's a girl's best friend? _______.</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
+  <si>
     <t>Fun tip! When your man asks you to go down on him, try surprising him with _______ instead.</t>
   </si>
   <si>
+    <t>B012</t>
+  </si>
+  <si>
+    <t>What is Batman's guilty pleasure? _______.</t>
+  </si>
+  <si>
+    <t>B013</t>
+  </si>
+  <si>
     <t>When Pharaoh remained unmoved, Moses called down a Plague of _______.</t>
   </si>
   <si>
+    <t>B014</t>
+  </si>
+  <si>
     <t>Airport security guidelines now prohibit _______ on airplanes.</t>
   </si>
   <si>
-    <t>That's right, I killed _______. How, you ask? _______ (PICK 2)</t>
-  </si>
-  <si>
-    <t>They said we were crazy. They said we couldn't put _______ inside of _______. They were wrong. (PICK 2)</t>
+    <t>B015</t>
+  </si>
+  <si>
+    <t>Once you pop, the fun don't stop! _______.</t>
+  </si>
+  <si>
+    <t>B016</t>
+  </si>
+  <si>
+    <t>That's why mums go to Iceland. _______.</t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t>What's my secret power? _______.</t>
+  </si>
+  <si>
+    <t>B019</t>
+  </si>
+  <si>
+    <t>Daddy, why is mummy crying? _______.</t>
+  </si>
+  <si>
+    <t>B021</t>
+  </si>
+  <si>
+    <t>How did I lose my virginity? _______.</t>
+  </si>
+  <si>
+    <t>B022</t>
   </si>
   <si>
     <t>White people like _______.</t>
   </si>
   <si>
+    <t>B023</t>
+  </si>
+  <si>
     <t>Here is the church. Here is the steeple. Open the doors, And there is _______.</t>
   </si>
   <si>
+    <t>B024</t>
+  </si>
+  <si>
     <t>_______? Jim'll fix it!</t>
   </si>
   <si>
+    <t>B025</t>
+  </si>
+  <si>
     <t>Hey Reddit! I'm _______. Ask me anything.</t>
   </si>
   <si>
+    <t>B026</t>
+  </si>
+  <si>
     <t>Next from J.K. Rowling: Harry Potter and the Chamber of _______.</t>
   </si>
   <si>
+    <t>B027</t>
+  </si>
+  <si>
+    <t>What made my first kiss so awkward? _______.</t>
+  </si>
+  <si>
+    <t>B028</t>
+  </si>
+  <si>
     <t>Uh, hey guys, I know this was my idea, but I'm having serious doubts about _______.</t>
   </si>
   <si>
-    <t>In a world ravaged by _______, our only solace is _______. (PICK 2)</t>
+    <t>B029</t>
+  </si>
+  <si>
+    <t>Why do I hurt all over? _______.</t>
+  </si>
+  <si>
+    <t>B031</t>
   </si>
   <si>
     <t>I get by with a little help from _______.</t>
   </si>
   <si>
+    <t>B032</t>
+  </si>
+  <si>
     <t>Next up on Channel 4: Ramsay's _______ Nightmares.</t>
   </si>
   <si>
+    <t>B033</t>
+  </si>
+  <si>
     <t>When I am Prime Minister of the United Kingdom, I will create the Ministry of _______.</t>
   </si>
   <si>
+    <t>B034</t>
+  </si>
+  <si>
     <t>Dear Agony Aunt, I'm having some trouble with _______ and I need your advice.</t>
   </si>
   <si>
+    <t>B035</t>
+  </si>
+  <si>
     <t>Maybe she's born with it. Maybe it's _______.</t>
   </si>
   <si>
+    <t>B036</t>
+  </si>
+  <si>
     <t>As the mum of five rambunctious boys, I'm no stranger to _______.</t>
   </si>
   <si>
+    <t>B037</t>
+  </si>
+  <si>
+    <t>Why is Alan so sweaty? _______.</t>
+  </si>
+  <si>
+    <t>B038</t>
+  </si>
+  <si>
     <t>UKIP: Putting _______ First!</t>
   </si>
   <si>
+    <t>B039</t>
+  </si>
+  <si>
+    <t>What will always get you laid? _______.</t>
+  </si>
+  <si>
+    <t>B040</t>
+  </si>
+  <si>
+    <t>What ended my last relationship? _______.</t>
+  </si>
+  <si>
+    <t>B041</t>
+  </si>
+  <si>
     <t>Just once, I'd like to hear you say "Thanks, Mum. Thanks for _______."</t>
   </si>
   <si>
-    <t>_______ is a slippery slope that leads to _______.</t>
+    <t>B042</t>
+  </si>
+  <si>
+    <t>What's there a ton of in heaven? _______.</t>
+  </si>
+  <si>
+    <t>B043</t>
+  </si>
+  <si>
+    <t>B044</t>
   </si>
   <si>
     <t>When I am a billionaire, I shall erect a 50-foot statue to commemorate _______.</t>
   </si>
   <si>
-    <t>Introducing the amazing superhero/ sidekick duo! It's _______ and _______! (PICK 2)</t>
+    <t>B046</t>
   </si>
   <si>
     <t>I got 99 problems but _______ ain't one.</t>
   </si>
   <si>
+    <t>B047</t>
+  </si>
+  <si>
+    <t>Why am I sticky? _______.</t>
+  </si>
+  <si>
+    <t>B048</t>
+  </si>
+  <si>
     <t>In Belmarsh Prison, word is you can trade 200 cigarettes for _______.</t>
   </si>
   <si>
+    <t>B049</t>
+  </si>
+  <si>
     <t>Just saw this upsetting video! Please retweet!! #stop_______.</t>
   </si>
   <si>
-    <t>Step 1: _______. Step 2: _______. Step 3: Profit. (PICK 2)</t>
+    <t>B051</t>
   </si>
   <si>
     <t>Alternative medicine is now embracing the curative powers of _______.</t>
   </si>
   <si>
+    <t>B052</t>
+  </si>
+  <si>
+    <t>What makes life worth living? _______.</t>
+  </si>
+  <si>
+    <t>B053</t>
+  </si>
+  <si>
+    <t>What's the next Happy Meal® toy? _______.</t>
+  </si>
+  <si>
+    <t>B054</t>
+  </si>
+  <si>
     <t>Hey guys, welcome to TGI Fridays! Would you like to start the night off right with _______?</t>
   </si>
   <si>
+    <t>B055</t>
+  </si>
+  <si>
+    <t>What's George W. Bush thinking about right now? _______.</t>
+  </si>
+  <si>
+    <t>B056</t>
+  </si>
+  <si>
     <t>_______: Kid-tested, mother-approved.</t>
   </si>
   <si>
+    <t>B057</t>
+  </si>
+  <si>
     <t>It's a trap! _______</t>
   </si>
   <si>
+    <t>B058</t>
+  </si>
+  <si>
     <t>If you can't be with the one you love, love _______.</t>
   </si>
   <si>
+    <t>B059</t>
+  </si>
+  <si>
     <t>The theme for next year's Eurovision Song Contest is "We are _______."</t>
   </si>
   <si>
+    <t>B060</t>
+  </si>
+  <si>
     <t>A romantic, candlelit dinner would be incomplete without _______.</t>
   </si>
   <si>
-    <t>When I was tripping on acid, _______ turned into _______. (PICK 2)</t>
+    <t>B062</t>
   </si>
   <si>
     <t>Now at the Natural History Museum: an interactive exhibit on _______.</t>
   </si>
   <si>
+    <t>B063</t>
+  </si>
+  <si>
     <t>Today on The Jeremy Kyle Show: "Help! My son is _______!"</t>
   </si>
   <si>
+    <t>B064</t>
+  </si>
+  <si>
     <t>During sex, I like to think about _______.</t>
   </si>
   <si>
-    <t>Channel 4 presents _______, the story of _______. (PICK 2)</t>
-  </si>
-  <si>
-    <t>I never truly understood _______ until I encountered _______. (PICK 2)</t>
+    <t>B067</t>
+  </si>
+  <si>
+    <t>What would grandma find disturbing, yet oddly charming? _______.</t>
+  </si>
+  <si>
+    <t>B068</t>
+  </si>
+  <si>
+    <t>What's that sound? _______.</t>
+  </si>
+  <si>
+    <t>B069</t>
   </si>
   <si>
     <t>How am I maintaining my relationship status? _______.</t>
   </si>
   <si>
+    <t>B070</t>
+  </si>
+  <si>
     <t>I'm no doctor, but I'm pretty sure what you're suffering from is called "_______."</t>
   </si>
   <si>
+    <t>B071</t>
+  </si>
+  <si>
+    <t>What never fails to liven up the party? _______.</t>
+  </si>
+  <si>
+    <t>B072</t>
+  </si>
+  <si>
+    <t>War! What is it good for? _______.</t>
+  </si>
+  <si>
+    <t>B073</t>
+  </si>
+  <si>
     <t>This is the way the world ends. This is the way the world ends. Not with a bang but with _______.</t>
   </si>
   <si>
+    <t>B074</t>
+  </si>
+  <si>
     <t>The school trip was completely ruined by _______.</t>
   </si>
   <si>
+    <t>B075</t>
+  </si>
+  <si>
     <t>Instead of coal, Father Christmas now gives bad children _______.</t>
   </si>
   <si>
+    <t>B076</t>
+  </si>
+  <si>
+    <t>Why can't I sleep at night? _______.</t>
+  </si>
+  <si>
+    <t>B077</t>
+  </si>
+  <si>
     <t>Well if you'll excuse me, gentlemen, I have a date with _______.</t>
   </si>
   <si>
+    <t>B078</t>
+  </si>
+  <si>
     <t>Netflix's new reality show features twelve hot singles living with _______.</t>
   </si>
   <si>
+    <t>B079</t>
+  </si>
+  <si>
+    <t>What gives me uncontrollable gas? _______.</t>
+  </si>
+  <si>
+    <t>B080</t>
+  </si>
+  <si>
     <t>I'm sorry, Sir, but I couldn't complete my homework because of _______.</t>
   </si>
   <si>
+    <t>B081</t>
+  </si>
+  <si>
     <t>This season at the Old Vic, Samuel Beckett's classic existential play, Waiting for _______.</t>
   </si>
   <si>
+    <t>B082</t>
+  </si>
+  <si>
     <t>That was so metal. _______</t>
   </si>
   <si>
-    <t>And the BAFTA for _______ goes to _______. (PICK 2)</t>
-  </si>
-  <si>
-    <t>For my next trick, I will pull _______ out of _______. (PICK 2)</t>
+    <t>B085</t>
   </si>
   <si>
     <t>Mr. and Mrs. Diaz, we called you in because we're concerned about Cynthia. Are you aware that your daughter is _______?</t>
   </si>
   <si>
+    <t>B086</t>
+  </si>
+  <si>
     <t>I drink to forget _______.</t>
   </si>
   <si>
+    <t>B087</t>
+  </si>
+  <si>
     <t>Next on Sky Sports: The World Championship of _______.</t>
   </si>
   <si>
@@ -228,9 +484,15 @@
     <t>Old MacDonald had _______. E-I-E-I-O.</t>
   </si>
   <si>
+    <t>What's that smell? _______.</t>
+  </si>
+  <si>
     <t>Kids, I don't need drugs to get high. I'm on high on _______.</t>
   </si>
   <si>
+    <t>What did I bring back from Amsterdam? _______.</t>
+  </si>
+  <si>
     <t>A recent laboratory study shows that undergraduates have 50% less sex after being exposed to _______.</t>
   </si>
   <si>
@@ -249,401 +511,61 @@
     <t>Click Here For _______!!!</t>
   </si>
   <si>
-    <t>Do NOT go here! Found _______ in my spaghetti bolognese!</t>
-  </si>
-  <si>
-    <t>B001</t>
-  </si>
-  <si>
-    <t>B002</t>
-  </si>
-  <si>
-    <t>B003</t>
-  </si>
-  <si>
-    <t>B004</t>
+    <t>type</t>
+  </si>
+  <si>
+    <t>card_text</t>
   </si>
   <si>
     <t>B005</t>
   </si>
   <si>
-    <t>B006</t>
-  </si>
-  <si>
-    <t>B007</t>
-  </si>
-  <si>
-    <t>B008</t>
-  </si>
-  <si>
-    <t>B009</t>
-  </si>
-  <si>
-    <t>B010</t>
-  </si>
-  <si>
-    <t>B011</t>
-  </si>
-  <si>
-    <t>B012</t>
-  </si>
-  <si>
-    <t>B013</t>
-  </si>
-  <si>
-    <t>B014</t>
-  </si>
-  <si>
-    <t>B015</t>
-  </si>
-  <si>
-    <t>B016</t>
-  </si>
-  <si>
     <t>B017</t>
   </si>
   <si>
-    <t>B018</t>
-  </si>
-  <si>
-    <t>B019</t>
-  </si>
-  <si>
     <t>B020</t>
   </si>
   <si>
-    <t>B021</t>
-  </si>
-  <si>
-    <t>B022</t>
-  </si>
-  <si>
-    <t>B023</t>
-  </si>
-  <si>
-    <t>B024</t>
-  </si>
-  <si>
-    <t>B025</t>
-  </si>
-  <si>
-    <t>B026</t>
-  </si>
-  <si>
-    <t>B027</t>
-  </si>
-  <si>
-    <t>B028</t>
-  </si>
-  <si>
-    <t>B029</t>
-  </si>
-  <si>
     <t>B030</t>
   </si>
   <si>
-    <t>B031</t>
-  </si>
-  <si>
-    <t>B032</t>
-  </si>
-  <si>
-    <t>B033</t>
-  </si>
-  <si>
-    <t>B034</t>
-  </si>
-  <si>
-    <t>B035</t>
-  </si>
-  <si>
-    <t>B036</t>
-  </si>
-  <si>
-    <t>B037</t>
-  </si>
-  <si>
-    <t>B038</t>
-  </si>
-  <si>
-    <t>B039</t>
-  </si>
-  <si>
-    <t>B040</t>
-  </si>
-  <si>
-    <t>B041</t>
-  </si>
-  <si>
-    <t>B042</t>
-  </si>
-  <si>
-    <t>B043</t>
-  </si>
-  <si>
-    <t>B044</t>
-  </si>
-  <si>
     <t>B045</t>
   </si>
   <si>
-    <t>B046</t>
-  </si>
-  <si>
-    <t>B047</t>
-  </si>
-  <si>
-    <t>B048</t>
-  </si>
-  <si>
-    <t>B049</t>
-  </si>
-  <si>
     <t>B050</t>
   </si>
   <si>
-    <t>B051</t>
-  </si>
-  <si>
-    <t>B052</t>
-  </si>
-  <si>
-    <t>B053</t>
-  </si>
-  <si>
-    <t>B054</t>
-  </si>
-  <si>
-    <t>B055</t>
-  </si>
-  <si>
-    <t>B056</t>
-  </si>
-  <si>
-    <t>B057</t>
-  </si>
-  <si>
-    <t>B058</t>
-  </si>
-  <si>
-    <t>B059</t>
-  </si>
-  <si>
-    <t>B060</t>
-  </si>
-  <si>
     <t>B061</t>
   </si>
   <si>
-    <t>B062</t>
-  </si>
-  <si>
-    <t>B063</t>
-  </si>
-  <si>
-    <t>B064</t>
-  </si>
-  <si>
     <t>B065</t>
   </si>
   <si>
     <t>B066</t>
   </si>
   <si>
-    <t>B067</t>
-  </si>
-  <si>
-    <t>B068</t>
-  </si>
-  <si>
-    <t>B069</t>
-  </si>
-  <si>
-    <t>B070</t>
-  </si>
-  <si>
-    <t>B071</t>
-  </si>
-  <si>
-    <t>B072</t>
-  </si>
-  <si>
-    <t>B073</t>
-  </si>
-  <si>
-    <t>B074</t>
-  </si>
-  <si>
-    <t>B075</t>
-  </si>
-  <si>
-    <t>B076</t>
-  </si>
-  <si>
-    <t>B077</t>
-  </si>
-  <si>
-    <t>B078</t>
-  </si>
-  <si>
-    <t>B079</t>
-  </si>
-  <si>
-    <t>B080</t>
-  </si>
-  <si>
-    <t>B081</t>
-  </si>
-  <si>
-    <t>B082</t>
-  </si>
-  <si>
     <t>B083</t>
   </si>
   <si>
     <t>B084</t>
-  </si>
-  <si>
-    <t>B085</t>
-  </si>
-  <si>
-    <t>B086</t>
-  </si>
-  <si>
-    <t>B087</t>
-  </si>
-  <si>
-    <t>B088</t>
-  </si>
-  <si>
-    <t>B089</t>
-  </si>
-  <si>
-    <t>B090</t>
-  </si>
-  <si>
-    <t>B091</t>
-  </si>
-  <si>
-    <t>B092</t>
-  </si>
-  <si>
-    <t>B093</t>
-  </si>
-  <si>
-    <t>B094</t>
-  </si>
-  <si>
-    <t>B095</t>
-  </si>
-  <si>
-    <t>B096</t>
-  </si>
-  <si>
-    <t>B097</t>
-  </si>
-  <si>
-    <t>B098</t>
-  </si>
-  <si>
-    <t>B099</t>
-  </si>
-  <si>
-    <t>B100</t>
-  </si>
-  <si>
-    <t>What are my parents hiding from me? _______.</t>
-  </si>
-  <si>
-    <t>What's a girl's best friend? _______.</t>
-  </si>
-  <si>
-    <t>What is Batman's guilty pleasure? _______.</t>
-  </si>
-  <si>
-    <t>That's why mums go to Iceland. _______.</t>
-  </si>
-  <si>
-    <t>What's my secret power? _______.</t>
-  </si>
-  <si>
-    <t>Daddy, why is mummy crying? _______.</t>
-  </si>
-  <si>
-    <t>How did I lose my virginity? _______.</t>
-  </si>
-  <si>
-    <t>What made my first kiss so awkward? _______.</t>
-  </si>
-  <si>
-    <t>Why do I hurt all over? _______.</t>
-  </si>
-  <si>
-    <t>Why is Alan so sweaty? _______.</t>
-  </si>
-  <si>
-    <t>What will always get you laid? _______.</t>
-  </si>
-  <si>
-    <t>What ended my last relationship? _______.</t>
-  </si>
-  <si>
-    <t>What's there a ton of in heaven? _______.</t>
-  </si>
-  <si>
-    <t>Why am I sticky? _______.</t>
-  </si>
-  <si>
-    <t>What makes life worth living? _______.</t>
-  </si>
-  <si>
-    <t>What's the next Happy Meal® toy? _______.</t>
-  </si>
-  <si>
-    <t>What's George W. Bush thinking about right now? _______.</t>
-  </si>
-  <si>
-    <t>What would grandma find disturbing, yet oddly charming? _______.</t>
-  </si>
-  <si>
-    <t>What's that sound? _______.</t>
-  </si>
-  <si>
-    <t>What never fails to liven up the party? _______.</t>
-  </si>
-  <si>
-    <t>War! What is it good for? _______.</t>
-  </si>
-  <si>
-    <t>Why can't I sleep at night? _______.</t>
-  </si>
-  <si>
-    <t>What gives me uncontrollable gas? _______.</t>
-  </si>
-  <si>
-    <t>Make a haiku. (PICK 3) _______. _______. _______.</t>
-  </si>
-  <si>
-    <t>What's that smell? _______.</t>
-  </si>
-  <si>
-    <t>What did I bring back from Amsterdam? _______.</t>
-  </si>
-  <si>
-    <t>Once you pop, the fun don't stop! _______.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="8"/>
@@ -660,7 +582,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -668,18 +590,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -702,44 +642,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -766,15 +706,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -801,7 +740,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -813,173 +751,196 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="92.5546875" customWidth="1"/>
+    <col min="2" max="2" width="83.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="A1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
@@ -987,791 +948,686 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>181</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>183</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>184</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="B54" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>191</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="B66" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B73" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s">
         <v>148</v>
-      </c>
-      <c r="B75" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="B77" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="B80" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B85" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
         <v>162</v>
       </c>
-      <c r="B89" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>163</v>
-      </c>
-      <c r="B90" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>164</v>
-      </c>
-      <c r="B91" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>165</v>
-      </c>
-      <c r="B92" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>166</v>
-      </c>
-      <c r="B93" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>167</v>
-      </c>
-      <c r="B94" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>168</v>
-      </c>
-      <c r="B95" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>169</v>
-      </c>
-      <c r="B96" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>170</v>
-      </c>
-      <c r="B97" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>171</v>
-      </c>
-      <c r="B98" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>172</v>
-      </c>
-      <c r="B99" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>173</v>
-      </c>
-      <c r="B100" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>174</v>
-      </c>
-      <c r="B101" t="s">
-        <v>73</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>